--- a/自考本科/自考课程/推荐的考试课程安排表.xlsx
+++ b/自考本科/自考课程/推荐的考试课程安排表.xlsx
@@ -140,18 +140,30 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Sarasa Mono SC"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Sarasa Mono SC"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -168,6 +180,26 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Sarasa Mono SC"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Sarasa Mono SC"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Sarasa Mono SC"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,6 +207,68 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="2"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color indexed="65"/>
@@ -191,39 +285,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -244,13 +307,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -259,13 +315,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color indexed="4"/>
@@ -274,25 +323,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -306,7 +338,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="2"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -345,25 +377,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="26"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -375,19 +461,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="26"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,133 +515,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="47"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,17 +643,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -650,15 +687,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -670,6 +698,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -697,262 +740,265 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="12" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="13" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="10" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" applyNumberFormat="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="9" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="12" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1217,887 +1263,887 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="9" style="6"/>
-    <col min="2" max="5" width="28.5777777777778" style="7" customWidth="1"/>
-    <col min="6" max="6" width="1.71111111111111" style="7" customWidth="1"/>
-    <col min="7" max="10" width="28.5777777777778" style="7" customWidth="1"/>
-    <col min="11" max="11" width="1.71111111111111" style="7" customWidth="1"/>
-    <col min="12" max="15" width="28.5777777777778" style="7" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="9" style="11"/>
+    <col min="2" max="5" width="28.5777777777778" style="12" customWidth="1"/>
+    <col min="6" max="6" width="1.71111111111111" style="12" customWidth="1"/>
+    <col min="7" max="10" width="28.5777777777778" style="12" customWidth="1"/>
+    <col min="11" max="11" width="1.71111111111111" style="12" customWidth="1"/>
+    <col min="12" max="15" width="28.5777777777778" style="12" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="8" t="s">
+    <row r="1" s="1" customFormat="1" ht="26.25" spans="1:15">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="G1" s="9" t="s">
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="G1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="L1" s="9" t="s">
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="L1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="8"/>
-      <c r="B2" s="10" t="s">
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="21.35" spans="1:15">
+      <c r="A2" s="13"/>
+      <c r="B2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="G2" s="27" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="G2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="L2" s="27" t="s">
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="L2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:15">
-      <c r="A3" s="8"/>
-      <c r="B3" s="11" t="s">
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+    </row>
+    <row r="3" s="3" customFormat="1" ht="14.6" spans="1:15">
+      <c r="A3" s="13"/>
+      <c r="B3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:15">
-      <c r="A4" s="8"/>
-      <c r="B4" s="12" t="s">
+    <row r="4" s="4" customFormat="1" ht="14.6" spans="1:15">
+      <c r="A4" s="13"/>
+      <c r="B4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="J4" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="N4" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="O4" s="17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="8"/>
-      <c r="B5" s="10" t="s">
+    <row r="5" s="2" customFormat="1" ht="21.35" spans="1:15">
+      <c r="A5" s="13"/>
+      <c r="B5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="G5" s="29" t="s">
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="G5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="L5" s="29" t="s">
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="L5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:15">
-      <c r="A6" s="8"/>
-      <c r="B6" s="11" t="s">
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+    </row>
+    <row r="6" s="3" customFormat="1" ht="14.6" spans="1:15">
+      <c r="A6" s="13"/>
+      <c r="B6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="29.25" spans="1:15">
-      <c r="A7" s="8"/>
-      <c r="B7" s="13" t="s">
+    <row r="7" s="4" customFormat="1" ht="29.25" spans="1:15">
+      <c r="A7" s="13"/>
+      <c r="B7" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="15" t="s">
+      <c r="L7" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="15" t="s">
+      <c r="N7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="15" t="s">
+      <c r="O7" s="20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:15">
-      <c r="A8" s="8"/>
-      <c r="B8" s="15" t="s">
+    <row r="8" s="4" customFormat="1" ht="14.6" spans="1:15">
+      <c r="A8" s="13"/>
+      <c r="B8" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="M8" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="N8" s="15" t="s">
+      <c r="N8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="O8" s="15" t="s">
+      <c r="O8" s="20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:15">
-      <c r="A9" s="8"/>
-      <c r="B9" s="15" t="s">
+    <row r="9" s="4" customFormat="1" ht="14.6" spans="1:15">
+      <c r="A9" s="13"/>
+      <c r="B9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="M9" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="15" t="s">
+      <c r="N9" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="O9" s="15" t="s">
+      <c r="O9" s="20" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:15">
-      <c r="A10" s="8"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="12" t="s">
+    <row r="10" s="4" customFormat="1" ht="14.6" spans="1:15">
+      <c r="A10" s="13"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="12" t="s">
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="12" t="s">
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="8"/>
-      <c r="B11" s="10" t="s">
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="21.35" spans="1:15">
+      <c r="A11" s="13"/>
+      <c r="B11" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="G11" s="29" t="s">
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="G11" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="L11" s="29" t="s">
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="L11" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:15">
-      <c r="A12" s="8"/>
-      <c r="B12" s="11" t="s">
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+    </row>
+    <row r="12" s="3" customFormat="1" ht="14.6" spans="1:15">
+      <c r="A12" s="13"/>
+      <c r="B12" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L12" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="M12" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N12" s="11" t="s">
+      <c r="N12" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="O12" s="16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="29.25" spans="1:15">
-      <c r="A13" s="8"/>
-      <c r="B13" s="15" t="s">
+    <row r="13" s="4" customFormat="1" ht="29.25" spans="1:15">
+      <c r="A13" s="13"/>
+      <c r="B13" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="L13" s="15" t="s">
+      <c r="L13" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N13" s="15" t="s">
+      <c r="N13" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="15" t="s">
+      <c r="O13" s="20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" spans="1:15">
-      <c r="A14" s="8"/>
-      <c r="B14" s="13" t="s">
+    <row r="14" s="4" customFormat="1" ht="14.6" spans="1:15">
+      <c r="A14" s="13"/>
+      <c r="B14" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="15" t="s">
+      <c r="J14" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="15" t="s">
+      <c r="L14" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="M14" s="15" t="s">
+      <c r="M14" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="N14" s="15" t="s">
+      <c r="N14" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="O14" s="15" t="s">
+      <c r="O14" s="20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:15">
-      <c r="A15" s="8"/>
-      <c r="B15" s="15" t="s">
+    <row r="15" s="4" customFormat="1" ht="14.6" spans="1:15">
+      <c r="A15" s="13"/>
+      <c r="B15" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="L15" s="15" t="s">
+      <c r="L15" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="M15" s="15" t="s">
+      <c r="M15" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="N15" s="15" t="s">
+      <c r="N15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="O15" s="15" t="s">
+      <c r="O15" s="20" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:15">
-      <c r="A16" s="8"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="12" t="s">
+    <row r="16" s="4" customFormat="1" ht="14.6" spans="1:15">
+      <c r="A16" s="13"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="12" t="s">
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="12" t="s">
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="N16" s="12"/>
-      <c r="O16" s="12"/>
-    </row>
-    <row r="17" s="3" customFormat="1" spans="1:15">
-      <c r="A17" s="18"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:15">
-      <c r="A18" s="8" t="s">
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+    </row>
+    <row r="17" s="5" customFormat="1" spans="1:15">
+      <c r="A17" s="23"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+    </row>
+    <row r="18" s="6" customFormat="1" ht="26.25" spans="1:15">
+      <c r="A18" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="G18" s="20" t="s">
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="G18" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="L18" s="20" t="s">
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="L18" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:15">
-      <c r="A19" s="8"/>
-      <c r="B19" s="10" t="s">
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+    </row>
+    <row r="19" s="7" customFormat="1" ht="21.35" spans="1:15">
+      <c r="A19" s="13"/>
+      <c r="B19" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10" t="s">
+      <c r="C19" s="15"/>
+      <c r="D19" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="10"/>
-      <c r="G19" s="10" t="s">
+      <c r="E19" s="15"/>
+      <c r="G19" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10" t="s">
+      <c r="H19" s="15"/>
+      <c r="I19" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J19" s="10"/>
-      <c r="L19" s="10" t="s">
+      <c r="J19" s="15"/>
+      <c r="L19" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10" t="s">
+      <c r="M19" s="15"/>
+      <c r="N19" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="O19" s="10"/>
-    </row>
-    <row r="20" s="2" customFormat="1" ht="43.9" spans="1:15">
-      <c r="A20" s="8"/>
-      <c r="B20" s="21" t="s">
+      <c r="O19" s="15"/>
+    </row>
+    <row r="20" s="4" customFormat="1" ht="43.9" spans="1:15">
+      <c r="A20" s="13"/>
+      <c r="B20" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="G20" s="30" t="s">
+      <c r="G20" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="21" t="s">
+      <c r="H20" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="I20" s="21" t="s">
+      <c r="I20" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="J20" s="21" t="s">
+      <c r="J20" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="L20" s="21" t="s">
+      <c r="L20" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="M20" s="21" t="s">
+      <c r="M20" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="N20" s="21" t="s">
+      <c r="N20" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="O20" s="21" t="s">
+      <c r="O20" s="26" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" s="4" customFormat="1" spans="1:5">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-    </row>
-    <row r="22" s="5" customFormat="1" spans="1:15">
-      <c r="A22" s="24" t="s">
+    <row r="21" s="8" customFormat="1" spans="1:5">
+      <c r="A21" s="27"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+    </row>
+    <row r="22" s="9" customFormat="1" ht="26.25" spans="1:15">
+      <c r="A22" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="G22" s="20" t="s">
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="G22" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="L22" s="20" t="s">
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="L22" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-    </row>
-    <row r="23" s="5" customFormat="1" spans="1:15">
-      <c r="A23" s="8"/>
-      <c r="B23" s="10" t="s">
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+    </row>
+    <row r="23" s="10" customFormat="1" ht="21.35" spans="1:15">
+      <c r="A23" s="13"/>
+      <c r="B23" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="G23" s="27" t="s">
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="G23" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="L23" s="27" t="s">
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="L23" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="8"/>
-      <c r="B24" s="11" t="s">
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+    </row>
+    <row r="24" ht="14.6" spans="1:15">
+      <c r="A24" s="13"/>
+      <c r="B24" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="J24" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L24" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="M24" s="11" t="s">
+      <c r="M24" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N24" s="11" t="s">
+      <c r="N24" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="O24" s="11" t="s">
+      <c r="O24" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" ht="14.65" spans="1:15">
-      <c r="A25" s="8"/>
-      <c r="B25" s="25" t="s">
+      <c r="A25" s="13"/>
+      <c r="B25" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="E25" s="26" t="s">
+      <c r="E25" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="32" t="s">
+      <c r="H25" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="I25" s="32" t="s">
+      <c r="I25" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="J25" s="32" t="s">
+      <c r="J25" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="L25" s="25" t="s">
+      <c r="L25" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="M25" s="26" t="s">
+      <c r="M25" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="N25" s="26" t="s">
+      <c r="N25" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="O25" s="26" t="s">
+      <c r="O25" s="31" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="8"/>
-      <c r="B26" s="10" t="s">
+    <row r="26" s="2" customFormat="1" ht="21.35" spans="1:15">
+      <c r="A26" s="13"/>
+      <c r="B26" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="G26" s="29" t="s">
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="G26" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="L26" s="29" t="s">
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+      <c r="L26" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27" s="8"/>
-      <c r="B27" s="11" t="s">
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="34"/>
+    </row>
+    <row r="27" ht="14.6" spans="1:15">
+      <c r="A27" s="13"/>
+      <c r="B27" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="J27" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="L27" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="M27" s="11" t="s">
+      <c r="M27" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N27" s="11" t="s">
+      <c r="N27" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="O27" s="11" t="s">
+      <c r="O27" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="28" ht="14.65" spans="1:15">
-      <c r="A28" s="8"/>
-      <c r="B28" s="25" t="s">
+      <c r="A28" s="13"/>
+      <c r="B28" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="E28" s="26" t="s">
+      <c r="E28" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="G28" s="25" t="s">
+      <c r="G28" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="26" t="s">
+      <c r="H28" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="I28" s="26" t="s">
+      <c r="I28" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="J28" s="26" t="s">
+      <c r="J28" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="L28" s="25" t="s">
+      <c r="L28" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="M28" s="26" t="s">
+      <c r="M28" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="N28" s="26" t="s">
+      <c r="N28" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="O28" s="26" t="s">
+      <c r="O28" s="31" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="32" spans="7:8">
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
     </row>
     <row r="33" spans="7:8">
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
     </row>
     <row r="34" spans="7:8">
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
     </row>
     <row r="35" spans="7:8">
-      <c r="G35" s="35"/>
-      <c r="H35" s="35"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
     </row>
     <row r="36" spans="7:8">
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
     </row>
     <row r="37" spans="7:8">
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="33">

--- a/自考本科/自考课程/推荐的考试课程安排表.xlsx
+++ b/自考本科/自考课程/推荐的考试课程安排表.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="37">
   <si>
     <t>自考科目</t>
   </si>
@@ -118,9 +118,6 @@
   </si>
   <si>
     <t>五月</t>
-  </si>
-  <si>
-    <t>五月（资料显示2～5日，具体时间后续参考后补充）</t>
   </si>
   <si>
     <t>03345-信息与网络安全管理</t>
@@ -141,9 +138,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -215,6 +212,14 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
@@ -222,8 +227,49 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color indexed="2"/>
+      <color indexed="4"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color indexed="20"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -237,9 +283,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -253,17 +298,36 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="2"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -276,75 +340,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color indexed="20"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color indexed="4"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -377,13 +374,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,7 +452,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,49 +500,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -461,103 +560,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="47"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,6 +655,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -666,23 +708,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -716,166 +743,142 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="9" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="13" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="13" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="11" applyNumberFormat="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="10" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="12" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="14" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
@@ -884,11 +887,11 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -967,28 +970,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1262,7 +1271,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="11"/>
@@ -1305,18 +1314,18 @@
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="L2" s="32" t="s">
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="L2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
     </row>
     <row r="3" s="3" customFormat="1" ht="14.6" spans="1:15">
       <c r="A3" s="13"/>
@@ -1371,16 +1380,16 @@
       <c r="E4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="I4" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="J4" s="32" t="s">
         <v>12</v>
       </c>
       <c r="L4" s="17" t="s">
@@ -1404,18 +1413,18 @@
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="L5" s="34" t="s">
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="L5" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="34"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="14.6" spans="1:15">
       <c r="A6" s="13"/>
@@ -1602,18 +1611,18 @@
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
-      <c r="G11" s="34" t="s">
+      <c r="G11" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="L11" s="34" t="s">
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="L11" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="14.6" spans="1:15">
       <c r="A12" s="13"/>
@@ -1865,10 +1874,10 @@
       <c r="D20" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="34" t="s">
         <v>29</v>
       </c>
       <c r="H20" s="26" t="s">
@@ -1931,219 +1940,141 @@
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
-      <c r="G23" s="32" t="s">
+      <c r="G23" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="L23" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+    </row>
+    <row r="24" ht="14.65" spans="1:15">
+      <c r="A24" s="13"/>
+      <c r="B24" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="L23" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32"/>
-      <c r="O23" s="32"/>
-    </row>
-    <row r="24" ht="14.6" spans="1:15">
-      <c r="A24" s="13"/>
-      <c r="B24" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I24" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="J24" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="M24" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="N24" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="O24" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" ht="14.65" spans="1:15">
+      <c r="C24" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="J24" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="L24" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="M24" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="N24" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="O24" s="39" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" ht="21.35" spans="1:15">
       <c r="A25" s="13"/>
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="G25" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="L25" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+    </row>
+    <row r="26" ht="14.65" spans="1:15">
+      <c r="A26" s="13"/>
+      <c r="B26" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="D26" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="31" t="s">
+      <c r="E26" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="E25" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="G25" s="36" t="s">
+      <c r="G26" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="37" t="s">
+      <c r="I26" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="I25" s="37" t="s">
+      <c r="J26" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="J25" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="L25" s="30" t="s">
+      <c r="L26" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="M26" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="M25" s="31" t="s">
+      <c r="N26" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="N25" s="31" t="s">
+      <c r="O26" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="O25" s="31" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" ht="21.35" spans="1:15">
-      <c r="A26" s="13"/>
-      <c r="B26" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="G26" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="L26" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
-      <c r="O26" s="34"/>
-    </row>
-    <row r="27" ht="14.6" spans="1:15">
-      <c r="A27" s="13"/>
-      <c r="B27" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I27" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="J27" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="M27" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="N27" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="O27" s="16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" ht="14.65" spans="1:15">
-      <c r="A28" s="13"/>
-      <c r="B28" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="G28" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="H28" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="I28" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="J28" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="L28" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="M28" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="N28" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="O28" s="31" t="s">
-        <v>37</v>
-      </c>
+    </row>
+    <row r="30" spans="7:8">
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+    </row>
+    <row r="31" spans="7:8">
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
     </row>
     <row r="32" spans="7:8">
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
     </row>
     <row r="33" spans="7:8">
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
     </row>
     <row r="34" spans="7:8">
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
     </row>
     <row r="35" spans="7:8">
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
-    </row>
-    <row r="36" spans="7:8">
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-    </row>
-    <row r="37" spans="7:8">
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="33">
@@ -2174,12 +2105,12 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="G23:J23"/>
     <mergeCell ref="L23:O23"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="L25:O25"/>
     <mergeCell ref="A1:A16"/>
     <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A22:A28"/>
+    <mergeCell ref="A22:A26"/>
   </mergeCells>
   <printOptions gridLines="1"/>
   <pageMargins left="0.700787401574803" right="0.700787401574803" top="0.751968503937008" bottom="0.751968503937008" header="0.3" footer="0.3"/>

--- a/自考本科/自考课程/推荐的考试课程安排表.xlsx
+++ b/自考本科/自考课程/推荐的考试课程安排表.xlsx
@@ -341,7 +341,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -370,12 +370,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.149998474074526"/>
         <bgColor theme="0" tint="-0.149998474074526"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -746,103 +740,103 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="9" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="13" applyNumberFormat="0" applyFont="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="13" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="8" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0">
@@ -857,7 +851,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
@@ -878,10 +872,10 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="14" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="14" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
@@ -891,7 +885,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -985,14 +979,8 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1964,10 +1952,10 @@
       <c r="D24" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="G24" s="36" t="s">
+      <c r="G24" s="35" t="s">
         <v>33</v>
       </c>
       <c r="H24" s="34" t="s">
@@ -1976,19 +1964,19 @@
       <c r="I24" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="J24" s="35" t="s">
+      <c r="J24" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="L24" s="38" t="s">
+      <c r="L24" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="M24" s="39" t="s">
+      <c r="M24" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="N24" s="39" t="s">
+      <c r="N24" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="O24" s="39" t="s">
+      <c r="O24" s="37" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2024,57 +2012,57 @@
       <c r="D26" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="37" t="s">
+      <c r="E26" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="G26" s="38" t="s">
+      <c r="G26" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="H26" s="39" t="s">
+      <c r="H26" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="I26" s="39" t="s">
+      <c r="I26" s="37" t="s">
         <v>35</v>
       </c>
       <c r="J26" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="L26" s="38" t="s">
+      <c r="L26" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="M26" s="39" t="s">
+      <c r="M26" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="N26" s="39" t="s">
+      <c r="N26" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="O26" s="39" t="s">
+      <c r="O26" s="37" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="30" spans="7:8">
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
     </row>
     <row r="31" spans="7:8">
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
     </row>
     <row r="32" spans="7:8">
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
     </row>
     <row r="33" spans="7:8">
-      <c r="G33" s="43"/>
-      <c r="H33" s="43"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
     </row>
     <row r="34" spans="7:8">
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
     </row>
     <row r="35" spans="7:8">
-      <c r="G35" s="42"/>
-      <c r="H35" s="42"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="33">
